--- a/414-rc---contact/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2635" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3069" uniqueCount="497">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T10:30:04+00:00</t>
+    <t>2026-01-27T15:50:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil de la ressource FRCoreRelatedPersonProfile permettant de représenter le contact PersonnePhyisique.</t>
+    <t>Profil de la ressource FRCoreRelatedPersonProfile permettant de représenter le contact PersonnePhysique.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1021,7 +1021,10 @@
     <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type|2.1.0</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-relation|2.2.0-ballot</t>
   </si>
   <si>
     <t>RelatedPerson.relationship:RelationType.id</t>
@@ -1058,6 +1061,51 @@
   </si>
   <si>
     <t>RelatedPerson.relationship:RelationType.text</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:LegalProtection</t>
+  </si>
+  <si>
+    <t>LegalProtection</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-protection-juridique|2.2.0-ballot</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:LegalProtection.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:LegalProtection.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:LegalProtection.coding</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:LegalProtection.coding.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:LegalProtection.coding.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:LegalProtection.coding.system</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R217-ProtectionJuridique/FHIR/TRE-R217-ProtectionJuridique</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:LegalProtection.coding.version</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:LegalProtection.coding.code</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:LegalProtection.coding.display</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:LegalProtection.coding.userSelected</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:LegalProtection.text</t>
   </si>
   <si>
     <t>RelatedPerson.name</t>
@@ -1120,9 +1168,6 @@
   </si>
   <si>
     <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
@@ -1807,12 +1852,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN72"/>
+  <dimension ref="A1:AN84"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.39453125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="51.32421875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="39.671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="13.1484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -6142,11 +6187,11 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>171</v>
+        <v>324</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6193,7 +6238,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>253</v>
@@ -6305,7 +6350,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>255</v>
@@ -6419,7 +6464,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>257</v>
@@ -6535,7 +6580,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>266</v>
@@ -6647,7 +6692,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>268</v>
@@ -6761,7 +6806,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>270</v>
@@ -6809,7 +6854,7 @@
         <v>77</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>77</v>
@@ -6877,7 +6922,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>280</v>
@@ -6991,7 +7036,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>288</v>
@@ -7105,7 +7150,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>296</v>
@@ -7219,7 +7264,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>304</v>
@@ -7335,7 +7380,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>313</v>
@@ -7451,12 +7496,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7465,7 +7512,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7474,22 +7521,20 @@
         <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>338</v>
+        <v>239</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>339</v>
+        <v>240</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>342</v>
+        <v>242</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7514,13 +7559,11 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>77</v>
+        <v>340</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7538,7 +7581,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>337</v>
+        <v>238</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7547,7 +7590,7 @@
         <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>99</v>
@@ -7556,21 +7599,21 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>343</v>
+        <v>245</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>77</v>
+        <v>246</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>344</v>
+        <v>247</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>345</v>
+        <v>253</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7679,10 +7722,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>346</v>
+        <v>255</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7793,14 +7836,12 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>77</v>
       </c>
@@ -7809,7 +7850,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
@@ -7818,19 +7859,23 @@
         <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>349</v>
+        <v>145</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>350</v>
+        <v>258</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
@@ -7878,7 +7923,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>115</v>
+        <v>262</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7890,27 +7935,27 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>77</v>
+        <v>263</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>77</v>
+        <v>264</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>352</v>
+        <v>266</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7927,26 +7972,22 @@
         <v>77</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>167</v>
+        <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>353</v>
+        <v>102</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
       </c>
@@ -7970,11 +8011,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="Y54" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>358</v>
+        <v>77</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -7992,7 +8035,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>359</v>
+        <v>104</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8004,38 +8047,38 @@
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>360</v>
+        <v>105</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>361</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>362</v>
+        <v>268</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -8044,23 +8087,21 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>363</v>
+        <v>109</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>364</v>
+        <v>110</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
       </c>
@@ -8096,59 +8137,59 @@
         <v>77</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>367</v>
+        <v>115</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>368</v>
+        <v>105</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>369</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>370</v>
+        <v>270</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>371</v>
+        <v>77</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>87</v>
@@ -8163,18 +8204,20 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>372</v>
+        <v>271</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>373</v>
+        <v>272</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8183,7 +8226,7 @@
         <v>77</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>77</v>
+        <v>347</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>77</v>
@@ -8222,7 +8265,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>375</v>
+        <v>276</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8240,32 +8283,32 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>376</v>
+        <v>277</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>377</v>
+        <v>278</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>378</v>
+        <v>280</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>379</v>
+        <v>77</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8280,13 +8323,13 @@
         <v>101</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>380</v>
+        <v>281</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>381</v>
+        <v>282</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>382</v>
+        <v>283</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8336,13 +8379,13 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>383</v>
+        <v>284</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
@@ -8351,24 +8394,24 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>384</v>
+        <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>385</v>
+        <v>285</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>386</v>
+        <v>286</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>387</v>
+        <v>349</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>387</v>
+        <v>288</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8391,16 +8434,18 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>101</v>
+        <v>167</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>388</v>
+        <v>289</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>389</v>
+        <v>290</v>
       </c>
       <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8424,11 +8469,13 @@
         <v>77</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="Y58" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z58" t="s" s="2">
-        <v>390</v>
+        <v>77</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
@@ -8446,13 +8493,13 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>391</v>
+        <v>292</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
@@ -8461,24 +8508,24 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>392</v>
+        <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>393</v>
+        <v>293</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>394</v>
+        <v>294</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>395</v>
+        <v>350</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>395</v>
+        <v>296</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8489,7 +8536,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
@@ -8504,13 +8551,15 @@
         <v>101</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>396</v>
+        <v>297</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>397</v>
+        <v>298</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8534,13 +8583,13 @@
         <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>398</v>
+        <v>77</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>399</v>
+        <v>77</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
@@ -8558,13 +8607,13 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
@@ -8576,21 +8625,21 @@
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>401</v>
+        <v>301</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>402</v>
+        <v>302</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>403</v>
+        <v>351</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>403</v>
+        <v>304</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8613,17 +8662,19 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>404</v>
+        <v>223</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>405</v>
+        <v>305</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O60" t="s" s="2">
-        <v>407</v>
+        <v>308</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8672,7 +8723,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>408</v>
+        <v>309</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8690,21 +8741,21 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>409</v>
+        <v>310</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>410</v>
+        <v>311</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>411</v>
+        <v>352</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>411</v>
+        <v>313</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8715,7 +8766,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
@@ -8724,22 +8775,22 @@
         <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>412</v>
+        <v>101</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>413</v>
+        <v>314</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>414</v>
+        <v>315</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>415</v>
+        <v>316</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>416</v>
+        <v>317</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8788,39 +8839,39 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>411</v>
+        <v>318</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>417</v>
+        <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>418</v>
+        <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>419</v>
+        <v>319</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>420</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>421</v>
+        <v>353</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>421</v>
+        <v>353</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8831,7 +8882,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>77</v>
@@ -8840,20 +8891,22 @@
         <v>77</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>167</v>
+        <v>354</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>422</v>
+        <v>355</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="O62" t="s" s="2">
-        <v>424</v>
+        <v>358</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -8878,11 +8931,13 @@
         <v>77</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
@@ -8900,39 +8955,39 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>421</v>
+        <v>353</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>426</v>
+        <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>427</v>
+        <v>359</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>428</v>
+        <v>360</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8952,16 +9007,16 @@
         <v>77</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>430</v>
+        <v>101</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>431</v>
+        <v>102</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>432</v>
+        <v>103</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9012,7 +9067,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>429</v>
+        <v>104</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9024,13 +9079,13 @@
         <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>433</v>
+        <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>434</v>
+        <v>105</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -9041,21 +9096,21 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>435</v>
+        <v>362</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>435</v>
+        <v>362</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>77</v>
@@ -9067,20 +9122,18 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>436</v>
+        <v>108</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>437</v>
+        <v>109</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>438</v>
+        <v>110</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>77</v>
       </c>
@@ -9116,19 +9169,19 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>435</v>
+        <v>115</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9137,32 +9190,34 @@
         <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>441</v>
+        <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>442</v>
+        <v>105</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>443</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>444</v>
+        <v>363</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="D65" t="s" s="2">
         <v>77</v>
       </c>
@@ -9171,7 +9226,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -9183,18 +9238,16 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>445</v>
+        <v>365</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>446</v>
+        <v>366</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>447</v>
+        <v>367</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>448</v>
-      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
       </c>
@@ -9242,7 +9295,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>444</v>
+        <v>115</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9254,27 +9307,27 @@
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>449</v>
+        <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>450</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>451</v>
+        <v>368</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>451</v>
+        <v>368</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9291,22 +9344,26 @@
         <v>77</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>404</v>
+        <v>167</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>452</v>
+        <v>369</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9330,13 +9387,11 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>77</v>
+        <v>373</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -9354,7 +9409,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>451</v>
+        <v>374</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9372,21 +9427,21 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>454</v>
+        <v>375</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>455</v>
+        <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>77</v>
+        <v>376</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>456</v>
+        <v>377</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>456</v>
+        <v>377</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9397,7 +9452,7 @@
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -9406,22 +9461,22 @@
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>457</v>
+        <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>458</v>
+        <v>378</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>459</v>
+        <v>379</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>460</v>
+        <v>380</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>461</v>
+        <v>381</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -9470,13 +9525,13 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>456</v>
+        <v>382</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
@@ -9488,25 +9543,25 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>462</v>
+        <v>383</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>77</v>
+        <v>384</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>463</v>
+        <v>385</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>463</v>
+        <v>385</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>77</v>
+        <v>386</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9522,18 +9577,20 @@
         <v>77</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>102</v>
+        <v>387</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9582,7 +9639,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>104</v>
+        <v>390</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9594,31 +9651,31 @@
         <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>105</v>
+        <v>391</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>77</v>
+        <v>392</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>464</v>
+        <v>393</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>464</v>
+        <v>393</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>107</v>
+        <v>394</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9634,19 +9691,19 @@
         <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>109</v>
+        <v>395</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>110</v>
+        <v>396</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>111</v>
+        <v>397</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9696,7 +9753,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>115</v>
+        <v>398</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9708,63 +9765,59 @@
         <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>77</v>
+        <v>399</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>105</v>
+        <v>400</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>77</v>
+        <v>401</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>465</v>
+        <v>402</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>465</v>
+        <v>402</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>466</v>
+        <v>77</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>467</v>
+        <v>403</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
       </c>
@@ -9788,13 +9841,11 @@
         <v>77</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>77</v>
+        <v>405</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>77</v>
@@ -9812,7 +9863,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>469</v>
+        <v>406</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9824,27 +9875,27 @@
         <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>77</v>
+        <v>407</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>190</v>
+        <v>408</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>77</v>
+        <v>409</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>470</v>
+        <v>410</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>470</v>
+        <v>410</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9852,10 +9903,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>77</v>
@@ -9864,23 +9915,19 @@
         <v>77</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>239</v>
+        <v>101</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>471</v>
+        <v>411</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
       </c>
@@ -9904,13 +9951,13 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>172</v>
+        <v>413</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>173</v>
+        <v>414</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>77</v>
@@ -9928,13 +9975,13 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>470</v>
+        <v>415</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>77</v>
@@ -9946,21 +9993,21 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>475</v>
+        <v>416</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>77</v>
+        <v>417</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>476</v>
+        <v>418</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>476</v>
+        <v>418</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9980,22 +10027,20 @@
         <v>77</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>223</v>
+        <v>419</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>477</v>
+        <v>420</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>479</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>480</v>
+        <v>422</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10044,7 +10089,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>476</v>
+        <v>423</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10062,12 +10107,1384 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Y74" s="2"/>
+      <c r="Z74" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AM72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN72" t="s" s="2">
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/414-rc---contact/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3069" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3105" uniqueCount="503">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T15:50:42+00:00</t>
+    <t>2026-01-28T14:07:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -667,6 +667,19 @@
     <t>commentaire</t>
   </si>
   <si>
+    <t>RelatedPerson.extension:description</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-related-person-contact-description|2.2.0-ballot}
+</t>
+  </si>
+  <si>
+    <t>Description du contact PersonnePhysique.</t>
+  </si>
+  <si>
     <t>RelatedPerson.modifierExtension</t>
   </si>
   <si>
@@ -1027,6 +1040,9 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-relation|2.2.0-ballot</t>
   </si>
   <si>
+    <t>Relation</t>
+  </si>
+  <si>
     <t>RelatedPerson.relationship:RelationType.id</t>
   </si>
   <si>
@@ -1223,6 +1239,9 @@
   </si>
   <si>
     <t>HumanName.family</t>
+  </si>
+  <si>
+    <t>nomNaissance</t>
   </si>
   <si>
     <t>./part[partType = FAM]</t>
@@ -1852,7 +1871,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN84"/>
+  <dimension ref="A1:AN85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.32421875" customWidth="true" bestFit="true"/>
@@ -4181,43 +4200,41 @@
         <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="D21" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>108</v>
+        <v>210</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O21" t="s" s="2">
         <v>211</v>
       </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
       </c>
@@ -4265,7 +4282,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4274,16 +4291,16 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>77</v>
+        <v>209</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -4294,43 +4311,45 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4379,7 +4398,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4391,27 +4410,27 @@
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>220</v>
+        <v>77</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4419,7 +4438,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>87</v>
@@ -4428,32 +4447,28 @@
         <v>77</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q23" t="s" s="2">
-        <v>228</v>
-      </c>
+      <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4497,13 +4512,13 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
@@ -4512,24 +4527,24 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>77</v>
+        <v>222</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>77</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4537,7 +4552,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>87</v>
@@ -4546,28 +4561,32 @@
         <v>77</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="P24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q24" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L24" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="P24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4611,10 +4630,10 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>87</v>
@@ -4629,21 +4648,21 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>77</v>
+        <v>234</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>237</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4651,10 +4670,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -4666,17 +4685,17 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4701,35 +4720,37 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>241</v>
+        <v>77</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="AC25" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
@@ -4741,25 +4762,23 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>246</v>
+        <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>77</v>
       </c>
@@ -4768,7 +4787,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4780,17 +4799,17 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4817,27 +4836,27 @@
       <c r="X26" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="Y26" s="2"/>
+      <c r="Y26" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4855,13 +4874,13 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27">
@@ -4869,9 +4888,11 @@
         <v>252</v>
       </c>
       <c r="B27" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="C27" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4889,19 +4910,21 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>101</v>
+        <v>243</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>102</v>
+        <v>254</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>103</v>
+        <v>245</v>
       </c>
       <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4925,13 +4948,11 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>77</v>
+        <v>255</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4949,50 +4970,50 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>104</v>
+        <v>242</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>105</v>
+        <v>249</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -5004,17 +5025,15 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5051,31 +5070,31 @@
         <v>77</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
@@ -5092,14 +5111,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5115,23 +5134,21 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>258</v>
+        <v>109</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>259</v>
+        <v>110</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
@@ -5167,19 +5184,19 @@
         <v>77</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>262</v>
+        <v>115</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5191,27 +5208,27 @@
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>263</v>
+        <v>105</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>264</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5222,7 +5239,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -5231,19 +5248,23 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>102</v>
+        <v>262</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
@@ -5291,50 +5312,50 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>105</v>
+        <v>267</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>77</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -5346,17 +5367,15 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5393,31 +5412,31 @@
         <v>77</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>77</v>
@@ -5434,21 +5453,21 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -5457,23 +5476,21 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>271</v>
+        <v>109</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>272</v>
+        <v>110</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5482,7 +5499,7 @@
         <v>77</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>77</v>
@@ -5509,51 +5526,51 @@
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>276</v>
+        <v>115</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>277</v>
+        <v>105</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>278</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5561,7 +5578,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>87</v>
@@ -5576,18 +5593,20 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5596,7 +5615,7 @@
         <v>77</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>77</v>
+        <v>279</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>77</v>
@@ -5635,7 +5654,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5653,21 +5672,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5690,18 +5709,18 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>167</v>
+        <v>101</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5749,7 +5768,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5767,21 +5786,21 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5804,17 +5823,17 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>101</v>
+        <v>167</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5863,7 +5882,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5881,21 +5900,21 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5918,19 +5937,17 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>223</v>
+        <v>101</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5979,7 +5996,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5997,21 +6014,21 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6034,19 +6051,19 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>101</v>
+        <v>227</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6095,7 +6112,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6113,25 +6130,23 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>77</v>
       </c>
@@ -6140,7 +6155,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -6152,17 +6167,19 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>239</v>
+        <v>101</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="O38" t="s" s="2">
-        <v>242</v>
+        <v>321</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6187,11 +6204,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>325</v>
+        <v>77</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6209,13 +6228,13 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>238</v>
+        <v>322</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
@@ -6227,23 +6246,25 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>245</v>
+        <v>323</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>246</v>
+        <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>247</v>
+        <v>324</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="B39" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>77</v>
       </c>
@@ -6252,7 +6273,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
@@ -6261,19 +6282,21 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>101</v>
+        <v>243</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>102</v>
+        <v>327</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>103</v>
+        <v>245</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
       </c>
@@ -6297,13 +6320,11 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>77</v>
+        <v>329</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -6321,50 +6342,50 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>104</v>
+        <v>242</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>77</v>
+        <v>330</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>105</v>
+        <v>249</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6376,17 +6397,15 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6423,31 +6442,31 @@
         <v>77</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
@@ -6464,14 +6483,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6487,23 +6506,21 @@
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>258</v>
+        <v>109</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>259</v>
+        <v>110</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
       </c>
@@ -6539,19 +6556,19 @@
         <v>77</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>262</v>
+        <v>115</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6563,27 +6580,27 @@
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>263</v>
+        <v>105</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>264</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6594,7 +6611,7 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
@@ -6603,19 +6620,23 @@
         <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>102</v>
+        <v>262</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6663,50 +6684,50 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>105</v>
+        <v>267</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>77</v>
+        <v>268</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6718,17 +6739,15 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6765,31 +6784,31 @@
         <v>77</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6806,21 +6825,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6829,23 +6848,21 @@
         <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>271</v>
+        <v>109</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>272</v>
+        <v>110</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
       </c>
@@ -6854,7 +6871,7 @@
         <v>77</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>332</v>
+        <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>77</v>
@@ -6881,51 +6898,51 @@
         <v>77</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>276</v>
+        <v>115</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>277</v>
+        <v>105</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>278</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6933,7 +6950,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>87</v>
@@ -6948,18 +6965,20 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
       </c>
@@ -6968,7 +6987,7 @@
         <v>77</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>77</v>
+        <v>337</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>77</v>
@@ -7007,7 +7026,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7025,21 +7044,21 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7062,18 +7081,18 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>167</v>
+        <v>101</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
       </c>
@@ -7121,7 +7140,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7139,21 +7158,21 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7176,17 +7195,17 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>101</v>
+        <v>167</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7235,7 +7254,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7253,21 +7272,21 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7290,19 +7309,17 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>223</v>
+        <v>101</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7351,7 +7368,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7369,21 +7386,21 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7406,19 +7423,19 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>101</v>
+        <v>227</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7467,7 +7484,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7485,25 +7502,23 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7524,17 +7539,19 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>239</v>
+        <v>101</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>240</v>
+        <v>318</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>242</v>
+        <v>321</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7559,11 +7576,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>340</v>
+        <v>77</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7581,13 +7600,13 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>238</v>
+        <v>322</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
@@ -7599,23 +7618,25 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>245</v>
+        <v>323</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>246</v>
+        <v>77</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>247</v>
+        <v>324</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7633,19 +7654,21 @@
         <v>77</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>101</v>
+        <v>243</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>102</v>
+        <v>244</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>103</v>
+        <v>245</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7669,13 +7692,11 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>77</v>
+        <v>345</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7693,50 +7714,50 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>104</v>
+        <v>242</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>77</v>
+        <v>330</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>105</v>
+        <v>249</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -7748,17 +7769,15 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7795,31 +7814,31 @@
         <v>77</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7836,14 +7855,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7859,23 +7878,21 @@
         <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>258</v>
+        <v>109</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>259</v>
+        <v>110</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
@@ -7911,19 +7928,19 @@
         <v>77</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>262</v>
+        <v>115</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7935,27 +7952,27 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>263</v>
+        <v>105</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>264</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7966,7 +7983,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -7975,19 +7992,23 @@
         <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>102</v>
+        <v>262</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
       </c>
@@ -8035,50 +8056,50 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>105</v>
+        <v>267</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>77</v>
+        <v>268</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -8090,17 +8111,15 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8137,31 +8156,31 @@
         <v>77</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
@@ -8178,21 +8197,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
@@ -8201,23 +8220,21 @@
         <v>77</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>271</v>
+        <v>109</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>272</v>
+        <v>110</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8226,7 +8243,7 @@
         <v>77</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>347</v>
+        <v>77</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>77</v>
@@ -8253,51 +8270,51 @@
         <v>77</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>276</v>
+        <v>115</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>277</v>
+        <v>105</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>278</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8305,7 +8322,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>87</v>
@@ -8320,18 +8337,20 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8340,7 +8359,7 @@
         <v>77</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>77</v>
+        <v>352</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>77</v>
@@ -8379,7 +8398,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8397,21 +8416,21 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8434,18 +8453,18 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>167</v>
+        <v>101</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8493,7 +8512,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8511,21 +8530,21 @@
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8548,17 +8567,17 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>101</v>
+        <v>167</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8607,7 +8626,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8625,21 +8644,21 @@
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8662,19 +8681,17 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>223</v>
+        <v>101</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8723,7 +8740,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8741,21 +8758,21 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8778,19 +8795,19 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>101</v>
+        <v>227</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8839,7 +8856,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8857,21 +8874,21 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>353</v>
+        <v>317</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8882,7 +8899,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>77</v>
@@ -8891,22 +8908,22 @@
         <v>77</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>354</v>
+        <v>101</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>355</v>
+        <v>318</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>356</v>
+        <v>319</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>357</v>
+        <v>320</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>358</v>
+        <v>321</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -8955,16 +8972,16 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>353</v>
+        <v>322</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>99</v>
@@ -8973,21 +8990,21 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>359</v>
+        <v>323</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>360</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8998,7 +9015,7 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>77</v>
@@ -9010,16 +9027,20 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>101</v>
+        <v>359</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>102</v>
+        <v>360</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
       </c>
@@ -9067,50 +9088,50 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>104</v>
+        <v>358</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>105</v>
+        <v>364</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>77</v>
+        <v>365</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>77</v>
@@ -9122,17 +9143,15 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9169,31 +9188,31 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
@@ -9210,23 +9229,21 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -9238,15 +9255,17 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>365</v>
+        <v>108</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>366</v>
+        <v>109</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9283,16 +9302,16 @@
         <v>77</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>115</v>
@@ -9313,7 +9332,7 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9327,9 +9346,11 @@
         <v>368</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="D66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9344,26 +9365,22 @@
         <v>77</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>167</v>
+        <v>370</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O66" t="s" s="2">
         <v>372</v>
       </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9387,11 +9404,13 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y66" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z66" t="s" s="2">
-        <v>373</v>
+        <v>77</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -9409,39 +9428,39 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>374</v>
+        <v>115</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>375</v>
+        <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>376</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9458,25 +9477,25 @@
         <v>77</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>101</v>
+        <v>167</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -9501,13 +9520,11 @@
         <v>77</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>77</v>
+        <v>378</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>77</v>
@@ -9525,7 +9542,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9543,25 +9560,25 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>386</v>
+        <v>77</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9583,15 +9600,17 @@
         <v>101</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
       </c>
@@ -9639,7 +9658,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9657,32 +9676,32 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>77</v>
@@ -9697,13 +9716,13 @@
         <v>101</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9753,13 +9772,13 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>77</v>
@@ -9768,35 +9787,35 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>77</v>
+        <v>400</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>77</v>
@@ -9811,12 +9830,14 @@
         <v>101</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M70" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9841,11 +9862,13 @@
         <v>77</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y70" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z70" t="s" s="2">
-        <v>405</v>
+        <v>77</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>77</v>
@@ -9863,7 +9886,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9878,24 +9901,24 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>409</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9906,7 +9929,7 @@
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>77</v>
@@ -9921,10 +9944,10 @@
         <v>101</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9951,13 +9974,11 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>77</v>
@@ -9975,7 +9996,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9990,24 +10011,24 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>77</v>
+        <v>413</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10018,7 +10039,7 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>77</v>
@@ -10030,18 +10051,16 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>419</v>
+        <v>101</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>422</v>
-      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>77</v>
       </c>
@@ -10065,13 +10084,13 @@
         <v>77</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>77</v>
+        <v>419</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>77</v>
+        <v>420</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -10089,13 +10108,13 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>77</v>
@@ -10107,21 +10126,21 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10132,7 +10151,7 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>77</v>
@@ -10141,22 +10160,20 @@
         <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="N73" s="2"/>
+      <c r="O73" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10205,39 +10222,39 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>432</v>
+        <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>433</v>
+        <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10248,7 +10265,7 @@
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>77</v>
@@ -10257,20 +10274,22 @@
         <v>77</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>167</v>
+        <v>433</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O74" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -10295,61 +10314,63 @@
         <v>77</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y74" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AL74" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AA74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK74" t="s" s="2">
+      <c r="AM74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>443</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10372,16 +10393,18 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="L75" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>77</v>
       </c>
@@ -10405,13 +10428,11 @@
         <v>77</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>77</v>
+        <v>446</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>77</v>
@@ -10429,7 +10450,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10444,16 +10465,16 @@
         <v>99</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AL75" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AL75" t="s" s="2">
+      <c r="AM75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="76">
@@ -10481,7 +10502,7 @@
         <v>77</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
         <v>451</v>
@@ -10492,12 +10513,8 @@
       <c r="M76" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="N76" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>455</v>
-      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
       </c>
@@ -10551,33 +10568,33 @@
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>458</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10588,7 +10605,7 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>77</v>
@@ -10600,17 +10617,19 @@
         <v>77</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10659,7 +10678,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10668,30 +10687,30 @@
         <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>77</v>
+        <v>462</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>465</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10702,7 +10721,7 @@
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>77</v>
@@ -10714,7 +10733,7 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>419</v>
+        <v>466</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>467</v>
@@ -10723,7 +10742,9 @@
         <v>468</v>
       </c>
       <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
       </c>
@@ -10771,13 +10792,13 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>77</v>
@@ -10789,21 +10810,21 @@
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>470</v>
+        <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>77</v>
+        <v>471</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10814,7 +10835,7 @@
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>77</v>
@@ -10826,7 +10847,7 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>472</v>
+        <v>425</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>473</v>
@@ -10834,12 +10855,8 @@
       <c r="M79" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="N79" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>476</v>
-      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>77</v>
       </c>
@@ -10887,13 +10904,13 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>77</v>
@@ -10905,10 +10922,10 @@
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>77</v>
+        <v>476</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>77</v>
@@ -10916,10 +10933,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10930,7 +10947,7 @@
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>77</v>
@@ -10942,16 +10959,20 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>101</v>
+        <v>478</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>102</v>
+        <v>479</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+        <v>480</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>77</v>
       </c>
@@ -10999,25 +11020,25 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>104</v>
+        <v>477</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>105</v>
+        <v>483</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -11028,21 +11049,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>77</v>
@@ -11054,17 +11075,15 @@
         <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -11113,19 +11132,19 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
@@ -11142,14 +11161,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>481</v>
+        <v>107</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11162,26 +11181,24 @@
         <v>77</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>482</v>
+        <v>109</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>483</v>
+        <v>110</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O82" t="s" s="2">
-        <v>211</v>
-      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>77</v>
       </c>
@@ -11229,7 +11246,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>484</v>
+        <v>115</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11247,7 +11264,7 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>190</v>
+        <v>105</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -11258,45 +11275,45 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>77</v>
+        <v>487</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>239</v>
+        <v>108</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>488</v>
+        <v>111</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>489</v>
+        <v>215</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
@@ -11321,13 +11338,13 @@
         <v>77</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>77</v>
@@ -11345,25 +11362,25 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>490</v>
+        <v>190</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
@@ -11385,7 +11402,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>87</v>
@@ -11400,7 +11417,7 @@
         <v>77</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="L84" t="s" s="2">
         <v>492</v>
@@ -11437,13 +11454,13 @@
         <v>77</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>77</v>
+        <v>171</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>77</v>
+        <v>173</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>77</v>
@@ -11464,7 +11481,7 @@
         <v>491</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>87</v>
@@ -11485,6 +11502,122 @@
         <v>77</v>
       </c>
       <c r="AN84" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/414-rc---contact/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T14:07:57+00:00</t>
+    <t>2026-01-29T08:29:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T08:29:40+00:00</t>
+    <t>2026-01-30T16:24:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil de la ressource FRCoreRelatedPersonProfile permettant de représenter le contact PersonnePhysique.</t>
+    <t>Profil de la ressource FRCoreRelatedPersonProfile permettant de représenter un contact de l'usager.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1037,10 +1037,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-relation|2.2.0-ballot</t>
-  </si>
-  <si>
-    <t>Relation</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-contact-relation|2.2.0-ballot</t>
+  </si>
+  <si>
+    <t>relation</t>
   </si>
   <si>
     <t>RelatedPerson.relationship:RelationType.id</t>
@@ -1085,7 +1085,7 @@
     <t>LegalProtection</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-protection-juridique|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-contact-protection-juridique|2.2.0-ballot</t>
   </si>
   <si>
     <t>RelatedPerson.relationship:LegalProtection.id</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T16:24:47+00:00</t>
+    <t>2026-02-02T09:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:56:46+00:00</t>
+    <t>2026-02-04T09:47:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -815,7 +815,10 @@
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role|2.1.0</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j384-role-membre-famille-ms</t>
   </si>
   <si>
     <t>RelatedPerson.relationship:Role.id</t>
@@ -1032,9 +1035,6 @@
   </si>
   <si>
     <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-contact-relation|2.2.0-ballot</t>
@@ -4948,11 +4948,11 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>171</v>
+        <v>255</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5111,10 +5111,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5225,10 +5225,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5254,16 +5254,16 @@
         <v>145</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5312,7 +5312,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5330,21 +5330,21 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5453,10 +5453,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5567,10 +5567,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5596,16 +5596,16 @@
         <v>129</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5615,7 +5615,7 @@
         <v>77</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>77</v>
@@ -5654,7 +5654,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5672,21 +5672,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5712,13 +5712,13 @@
         <v>101</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5768,7 +5768,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5786,21 +5786,21 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5826,14 +5826,14 @@
         <v>167</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5882,7 +5882,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5900,21 +5900,21 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5940,14 +5940,14 @@
         <v>101</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5996,7 +5996,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6014,21 +6014,21 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6054,16 +6054,16 @@
         <v>227</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6112,7 +6112,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6130,21 +6130,21 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6170,16 +6170,16 @@
         <v>101</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6228,7 +6228,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6246,24 +6246,24 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>242</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>77</v>
@@ -6288,7 +6288,7 @@
         <v>243</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M39" t="s" s="2">
         <v>245</v>
@@ -6320,7 +6320,7 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>328</v>
+        <v>255</v>
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
@@ -6374,7 +6374,7 @@
         <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6486,7 +6486,7 @@
         <v>332</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6600,7 +6600,7 @@
         <v>333</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6626,16 +6626,16 @@
         <v>145</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6684,7 +6684,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6702,13 +6702,13 @@
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="43">
@@ -6716,7 +6716,7 @@
         <v>334</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6828,7 +6828,7 @@
         <v>335</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6942,7 +6942,7 @@
         <v>336</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6968,16 +6968,16 @@
         <v>129</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -7026,7 +7026,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7044,13 +7044,13 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="46">
@@ -7058,7 +7058,7 @@
         <v>338</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7084,13 +7084,13 @@
         <v>101</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7140,7 +7140,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7158,13 +7158,13 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="47">
@@ -7172,7 +7172,7 @@
         <v>339</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7198,14 +7198,14 @@
         <v>167</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7254,7 +7254,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7272,13 +7272,13 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="48">
@@ -7286,7 +7286,7 @@
         <v>340</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7312,14 +7312,14 @@
         <v>101</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7368,7 +7368,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7386,13 +7386,13 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49">
@@ -7400,7 +7400,7 @@
         <v>341</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7426,16 +7426,16 @@
         <v>227</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7484,7 +7484,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7502,13 +7502,13 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50">
@@ -7516,7 +7516,7 @@
         <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7542,16 +7542,16 @@
         <v>101</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7600,7 +7600,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7618,13 +7618,13 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="51">
@@ -7692,7 +7692,7 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>328</v>
+        <v>255</v>
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
@@ -7746,7 +7746,7 @@
         <v>346</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7858,7 +7858,7 @@
         <v>347</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7972,7 +7972,7 @@
         <v>348</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7998,16 +7998,16 @@
         <v>145</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8056,7 +8056,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8074,13 +8074,13 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="55">
@@ -8088,7 +8088,7 @@
         <v>349</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8200,7 +8200,7 @@
         <v>350</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8314,7 +8314,7 @@
         <v>351</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8340,16 +8340,16 @@
         <v>129</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8398,7 +8398,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8416,13 +8416,13 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="58">
@@ -8430,7 +8430,7 @@
         <v>353</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8456,13 +8456,13 @@
         <v>101</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8512,7 +8512,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8530,13 +8530,13 @@
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="59">
@@ -8544,7 +8544,7 @@
         <v>354</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8570,14 +8570,14 @@
         <v>167</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8626,7 +8626,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8644,13 +8644,13 @@
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="60">
@@ -8658,7 +8658,7 @@
         <v>355</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8684,14 +8684,14 @@
         <v>101</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8740,7 +8740,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8758,13 +8758,13 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="61">
@@ -8772,7 +8772,7 @@
         <v>356</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8798,16 +8798,16 @@
         <v>227</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8856,7 +8856,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8874,13 +8874,13 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="62">
@@ -8888,7 +8888,7 @@
         <v>357</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8914,16 +8914,16 @@
         <v>101</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -8972,7 +8972,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8990,13 +8990,13 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63">
@@ -9520,7 +9520,7 @@
         <v>77</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>328</v>
+        <v>255</v>
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
@@ -9974,7 +9974,7 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>328</v>
+        <v>255</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
@@ -10428,7 +10428,7 @@
         <v>77</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>328</v>
+        <v>255</v>
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">

--- a/414-rc---contact/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3105" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3104" uniqueCount="503">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T09:47:16+00:00</t>
+    <t>2026-02-04T14:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -790,7 +790,10 @@
     <t>We need to know the relationship with the patient since it influences the interpretation of the information attributed to this person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype|4.0.1</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-contact-related-person-relashionship|2.2.0-ballot</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -813,9 +816,6 @@
   </si>
   <si>
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j384-role-membre-famille-ms</t>
@@ -4834,19 +4834,17 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
@@ -4874,24 +4872,24 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>242</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -4916,7 +4914,7 @@
         <v>243</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M27" t="s" s="2">
         <v>245</v>
@@ -4948,7 +4946,7 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
@@ -4988,13 +4986,13 @@
         <v>85</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="28">
@@ -6320,7 +6318,7 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
@@ -6360,13 +6358,13 @@
         <v>330</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40">
@@ -7692,7 +7690,7 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
@@ -7732,13 +7730,13 @@
         <v>330</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="52">
@@ -9520,7 +9518,7 @@
         <v>77</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
@@ -9974,7 +9972,7 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
@@ -10428,7 +10426,7 @@
         <v>77</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">

--- a/414-rc---contact/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T14:08:59+00:00</t>
+    <t>2026-02-04T16:27:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
